--- a/data/trans_orig/P1806_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023</t>
+          <t>Población según si en los últimos 12 meses han visitado un podólogo en 2023 (tasa de respuesta: 99,98%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10723</t>
+          <t>11255</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28631</t>
+          <t>27634</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>19191</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36338</t>
+          <t>35519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33401</t>
+          <t>33974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>56004</t>
+          <t>59421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>476581</t>
+          <t>477578</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>494489</t>
+          <t>493957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>411129</t>
+          <t>411948</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428835</t>
+          <t>428276</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>896675</t>
+          <t>893258</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>919278</t>
+          <t>918705</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,43%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9454</t>
+          <t>9609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23892</t>
+          <t>23658</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19230</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>36635</t>
+          <t>36073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>32040</t>
+          <t>31911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54760</t>
+          <t>53663</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,43%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428321</t>
+          <t>428555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442759</t>
+          <t>442604</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>345945</t>
+          <t>346507</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>363413</t>
+          <t>363350</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,99%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>780033</t>
+          <t>781130</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>802753</t>
+          <t>802882</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,18%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1020</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12840</t>
+          <t>13135</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8559</t>
+          <t>8532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>19029</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>8022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29701</t>
+          <t>29860</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,58%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655424</t>
+          <t>655129</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>667244</t>
+          <t>666991</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>148449</t>
+          <t>147882</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158352</t>
+          <t>158379</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>805474</t>
+          <t>805315</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827274</t>
+          <t>827153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,04%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34131</t>
+          <t>35678</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>19234</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53326</t>
+          <t>54382</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42076</t>
+          <t>41002</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78831</t>
+          <t>78532</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1000688</t>
+          <t>999141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1020236</t>
+          <t>1019784</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,59%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>924202</t>
+          <t>923146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>958605</t>
+          <t>958294</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1933516</t>
+          <t>1933815</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1970271</t>
+          <t>1971345</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,08%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,96%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3157</t>
+          <t>3088</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12434</t>
+          <t>12052</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>26583</t>
+          <t>27153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>48635</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33652</t>
+          <t>33862</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56341</t>
+          <t>56128</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462612</t>
+          <t>462994</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471889</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>792700</t>
+          <t>791874</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>814752</t>
+          <t>814182</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1260040</t>
+          <t>1260253</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1282729</t>
+          <t>1282519</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,43%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>18799</t>
+          <t>20107</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21040</t>
+          <t>21655</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40596</t>
+          <t>41884</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26780</t>
+          <t>26180</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53557</t>
+          <t>51686</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>221708</t>
+          <t>220400</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238489</t>
+          <t>238212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,18%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>720096</t>
+          <t>718808</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>739652</t>
+          <t>739037</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>947643</t>
+          <t>949514</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>974420</t>
+          <t>975020</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>57877</t>
+          <t>56017</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>96786</t>
+          <t>97437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>139005</t>
+          <t>140970</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>196144</t>
+          <t>197797</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>209788</t>
+          <t>210981</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>281616</t>
+          <t>280848</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,04%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3279274</t>
+          <t>3278623</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3318183</t>
+          <t>3320043</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3380370</t>
+          <t>3378717</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3437509</t>
+          <t>3435544</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6670958</t>
+          <t>6671726</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6742786</t>
+          <t>6741593</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,96%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1806_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P1806_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>17847</t>
+          <t>18161</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11255</t>
+          <t>11127</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27634</t>
+          <t>29677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>26214</t>
+          <t>27306</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>19191</t>
+          <t>19998</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35519</t>
+          <t>37641</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>44061</t>
+          <t>45467</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33974</t>
+          <t>35566</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>59421</t>
+          <t>59461</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,72%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>487365</t>
+          <t>532457</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>477578</t>
+          <t>520941</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>493957</t>
+          <t>539491</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,47%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>421253</t>
+          <t>461105</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>411948</t>
+          <t>450770</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>428276</t>
+          <t>468413</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,06%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>908618</t>
+          <t>993562</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>893258</t>
+          <t>979568</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>918705</t>
+          <t>1003463</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,102 +1068,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>15500</t>
+          <t>16400</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9609</t>
+          <t>9927</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23658</t>
+          <t>26231</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>5,43%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>31022</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>22932</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>40851</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7,33%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,65%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>47422</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>36021</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>59190</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>5,23%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>26713</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>19230</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>36073</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,98%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>5,03%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,43%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>42213</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>31911</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>53663</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>5,06%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -1181,102 +1181,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>436713</t>
+          <t>466812</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>428555</t>
+          <t>456981</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>442604</t>
+          <t>473285</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>94,57%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,95%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>545</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>392121</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>382292</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>400211</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>92,67%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>90,35%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>94,58%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1006</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>858933</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>847165</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>870334</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
           <t>94,77%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>355867</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>346507</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>363350</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>93,02%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>90,57%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>94,97%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1006</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>792580</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>781130</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>802882</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>94,94%</t>
-        </is>
-      </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,03%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5957</t>
+          <t>6094</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>2721</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13135</t>
+          <t>12382</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>13019</t>
+          <t>14097</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>8532</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19029</t>
+          <t>21384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>18976</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8022</t>
+          <t>13335</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>29860</t>
+          <t>28449</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>662307</t>
+          <t>465518</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>655129</t>
+          <t>459230</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>666991</t>
+          <t>468891</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,81%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>153892</t>
+          <t>173400</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>147882</t>
+          <t>166113</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>158379</t>
+          <t>178217</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,48%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>816199</t>
+          <t>638918</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>805315</t>
+          <t>630660</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>827153</t>
+          <t>645774</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>97,98%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>24619</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15035</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35678</t>
+          <t>35903</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>38740</t>
+          <t>41555</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>19234</t>
+          <t>31530</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54382</t>
+          <t>51913</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61585</t>
+          <t>66174</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>41002</t>
+          <t>53231</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>78532</t>
+          <t>82134</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,12%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1011974</t>
+          <t>1107224</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>999141</t>
+          <t>1095940</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1019784</t>
+          <t>1115952</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>938788</t>
+          <t>819060</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>923146</t>
+          <t>808702</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>958294</t>
+          <t>829085</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,44%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>96,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1950762</t>
+          <t>1926284</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1933815</t>
+          <t>1910324</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1971345</t>
+          <t>1939227</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,96%</t>
+          <t>97,33%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>977528</t>
+          <t>860615</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2012347</t>
+          <t>1992458</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3088</t>
+          <t>2896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>11990</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>37781</t>
+          <t>40495</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>31839</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>49461</t>
+          <t>50735</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>44072</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>33862</t>
+          <t>36457</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>56128</t>
+          <t>57793</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,13%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>468755</t>
+          <t>561690</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>462994</t>
+          <t>555974</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>565068</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>803554</t>
+          <t>790355</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>791874</t>
+          <t>780115</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>814182</t>
+          <t>799011</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1272309</t>
+          <t>1352045</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1260253</t>
+          <t>1341021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1282519</t>
+          <t>1362357</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,39%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>841335</t>
+          <t>830850</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1316381</t>
+          <t>1398814</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>7735</t>
+          <t>6802</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>19307</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29481</t>
+          <t>31238</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21655</t>
+          <t>22910</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41884</t>
+          <t>43708</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>37216</t>
+          <t>38040</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>26180</t>
+          <t>27134</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>51686</t>
+          <t>51947</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>232772</t>
+          <t>230426</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>220400</t>
+          <t>217921</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>238212</t>
+          <t>235521</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>91,64%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>731211</t>
+          <t>812358</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>718808</t>
+          <t>799888</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>739037</t>
+          <t>820686</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,15%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>963984</t>
+          <t>1042784</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>949514</t>
+          <t>1028877</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>975020</t>
+          <t>1053690</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>95,19%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>97,39%</t>
+          <t>97,49%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>240507</t>
+          <t>237228</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>760692</t>
+          <t>843596</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>1001200</t>
+          <t>1080824</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>76175</t>
+          <t>78351</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>56017</t>
+          <t>61757</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>97437</t>
+          <t>97561</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>171949</t>
+          <t>185714</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>140970</t>
+          <t>166337</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>197797</t>
+          <t>208538</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>248124</t>
+          <t>264064</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>210981</t>
+          <t>236270</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>280848</t>
+          <t>294700</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3299885</t>
+          <t>3364125</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3278623</t>
+          <t>3344915</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3320043</t>
+          <t>3380719</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3404565</t>
+          <t>3448398</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3378717</t>
+          <t>3425574</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3435544</t>
+          <t>3467775</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,42%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6704450</t>
+          <t>6812524</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>6671726</t>
+          <t>6781888</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>6741593</t>
+          <t>6840318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,66%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>3376060</t>
+          <t>3442476</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>3576514</t>
+          <t>3634112</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>6952574</t>
+          <t>7076588</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
